--- a/network_specialist/status.xlsx
+++ b/network_specialist/status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\security_specialist\network_tech\network_specialist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0867F71F-2FD4-435B-8A6D-120B54267819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94192F5B-7143-4BEE-80FA-06E497062C5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11820" yWindow="840" windowWidth="15330" windowHeight="14310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -421,6 +421,28 @@
       </c>
       <c r="C3">
         <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/network_specialist/status.xlsx
+++ b/network_specialist/status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\security_specialist\network_tech\network_specialist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94192F5B-7143-4BEE-80FA-06E497062C5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD1EA62A-E83C-454D-BD14-62697AEA34DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="19215" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -445,6 +445,28 @@
         <v>30</v>
       </c>
     </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
